--- a/ML_lab/Book001.xlsx
+++ b/ML_lab/Book001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bca\Desktop\vault\ML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9526CB2-4F72-4297-9116-56285618A90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4950FF0-43BC-44B0-8CAD-C99378F4C0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="15600" xr2:uid="{08CA13EA-14CB-4CDB-8A21-888E9D7579B2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
   <si>
     <t>Name</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Gopal</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
     <t>Bengaluru</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>Claudia</t>
   </si>
   <si>
-    <t>Tiedamen</t>
-  </si>
-  <si>
     <t>Jonas</t>
   </si>
   <si>
@@ -98,9 +92,6 @@
     <t>Angel</t>
   </si>
   <si>
-    <t>F</t>
-  </si>
-  <si>
     <t xml:space="preserve">Winden </t>
   </si>
   <si>
@@ -116,13 +107,25 @@
     <t>German</t>
   </si>
   <si>
-    <t>Pensylvenia</t>
-  </si>
-  <si>
-    <t>Babi</t>
-  </si>
-  <si>
-    <t>Tirupati</t>
+    <t>Marks</t>
+  </si>
+  <si>
+    <t>Pensylvania</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>TiedaMaleen</t>
+  </si>
+  <si>
+    <t>Shibu</t>
+  </si>
+  <si>
+    <t>Sajan rao</t>
   </si>
 </sst>
 </file>
@@ -494,217 +497,262 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F98AAC01-803C-4744-A06B-3CA0D4835525}">
-  <dimension ref="A2:D16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
       <c r="B6">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="E6">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
       <c r="B7">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="E7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
       <c r="B8">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9">
+        <v>94</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9">
-        <v>87</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="E11">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15">
         <v>20</v>
       </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10">
-        <v>94</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12">
-        <v>43</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13">
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" t="s">
         <v>29</v>
       </c>
-      <c r="C13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15">
-        <v>17</v>
-      </c>
-      <c r="C15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" t="s">
-        <v>28</v>
+      <c r="E15">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
